--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -18864,6 +18864,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="805">
+      <c r="A805" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B805" t="n">
+        <v>0</v>
+      </c>
+      <c r="C805" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="D805" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="E805" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="F805" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="G805" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B806" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C806" t="n">
+        <v>0.40599998831749</v>
+      </c>
+      <c r="D806" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="E806" t="n">
+        <v>0.40599998831749</v>
+      </c>
+      <c r="F806" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G806" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -18910,6 +18910,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="807">
+      <c r="A807" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B807" t="n">
+        <v>37500</v>
+      </c>
+      <c r="C807" t="n">
+        <v>0.404000014066696</v>
+      </c>
+      <c r="D807" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="E807" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="F807" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="G807" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -18933,6 +18933,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="808">
+      <c r="A808" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B808" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C808" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="D808" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="E808" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F808" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G808" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -18774,22 +18774,22 @@
     </row>
     <row r="801">
       <c r="A801" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B801" t="n">
-        <v>1500</v>
+        <v>61500</v>
       </c>
       <c r="C801" t="n">
-        <v>0.40599998831749</v>
+        <v>0.437999993562698</v>
       </c>
       <c r="D801" t="n">
-        <v>0.40599998831749</v>
+        <v>0.409999996423721</v>
       </c>
       <c r="E801" t="n">
-        <v>0.40599998831749</v>
+        <v>0.437999993562698</v>
       </c>
       <c r="F801" t="n">
-        <v>0.40599998831749</v>
+        <v>0.414000004529953</v>
       </c>
       <c r="G801" t="s">
         <v>7</v>
@@ -18797,10 +18797,10 @@
     </row>
     <row r="802">
       <c r="A802" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B802" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="C802" t="n">
         <v>0.40599998831749</v>
@@ -18820,7 +18820,7 @@
     </row>
     <row r="803">
       <c r="A803" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B803" t="n">
         <v>0</v>
@@ -18843,22 +18843,22 @@
     </row>
     <row r="804">
       <c r="A804" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B804" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="C804" t="n">
-        <v>0.414000004529953</v>
+        <v>0.40599998831749</v>
       </c>
       <c r="D804" t="n">
-        <v>0.412000000476837</v>
+        <v>0.40599998831749</v>
       </c>
       <c r="E804" t="n">
-        <v>0.414000004529953</v>
+        <v>0.40599998831749</v>
       </c>
       <c r="F804" t="n">
-        <v>0.412000000476837</v>
+        <v>0.40599998831749</v>
       </c>
       <c r="G804" t="s">
         <v>7</v>
@@ -18866,19 +18866,19 @@
     </row>
     <row r="805">
       <c r="A805" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B805" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="C805" t="n">
-        <v>0.412000000476837</v>
+        <v>0.414000004529953</v>
       </c>
       <c r="D805" t="n">
         <v>0.412000000476837</v>
       </c>
       <c r="E805" t="n">
-        <v>0.412000000476837</v>
+        <v>0.414000004529953</v>
       </c>
       <c r="F805" t="n">
         <v>0.412000000476837</v>
@@ -18889,22 +18889,22 @@
     </row>
     <row r="806">
       <c r="A806" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B806" t="n">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="C806" t="n">
-        <v>0.40599998831749</v>
+        <v>0.412000000476837</v>
       </c>
       <c r="D806" t="n">
-        <v>0.400000005960464</v>
+        <v>0.412000000476837</v>
       </c>
       <c r="E806" t="n">
-        <v>0.40599998831749</v>
+        <v>0.412000000476837</v>
       </c>
       <c r="F806" t="n">
-        <v>0.400000005960464</v>
+        <v>0.412000000476837</v>
       </c>
       <c r="G806" t="s">
         <v>7</v>
@@ -18912,22 +18912,22 @@
     </row>
     <row r="807">
       <c r="A807" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B807" t="n">
-        <v>37500</v>
+        <v>30000</v>
       </c>
       <c r="C807" t="n">
-        <v>0.404000014066696</v>
+        <v>0.40599998831749</v>
       </c>
       <c r="D807" t="n">
         <v>0.400000005960464</v>
       </c>
       <c r="E807" t="n">
-        <v>0.40200001001358</v>
+        <v>0.40599998831749</v>
       </c>
       <c r="F807" t="n">
-        <v>0.40200001001358</v>
+        <v>0.400000005960464</v>
       </c>
       <c r="G807" t="s">
         <v>7</v>
@@ -18935,24 +18935,47 @@
     </row>
     <row r="808">
       <c r="A808" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B808" t="n">
-        <v>7500</v>
+        <v>37500</v>
       </c>
       <c r="C808" t="n">
-        <v>0.400000005960464</v>
+        <v>0.404000014066696</v>
       </c>
       <c r="D808" t="n">
         <v>0.400000005960464</v>
       </c>
       <c r="E808" t="n">
-        <v>0.400000005960464</v>
+        <v>0.40200001001358</v>
       </c>
       <c r="F808" t="n">
-        <v>0.400000005960464</v>
+        <v>0.40200001001358</v>
       </c>
       <c r="G808" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B809" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C809" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D809" t="n">
+        <v>0.404000014066696</v>
+      </c>
+      <c r="E809" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="F809" t="n">
+        <v>0.404000014066696</v>
+      </c>
+      <c r="G809" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -21446,7 +21446,7 @@
         <v>0.40200001001358</v>
       </c>
       <c r="D811" t="n">
-        <v>0.400000005960464</v>
+        <v>0.398000001907349</v>
       </c>
       <c r="E811" t="n">
         <v>0.40200001001358</v>
@@ -21458,6 +21458,32 @@
         <v>0.398000001907349</v>
       </c>
       <c r="H811" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B812" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C812" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="D812" t="n">
+        <v>0.38400000333786</v>
+      </c>
+      <c r="E812" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F812" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="G812" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="H812" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -21487,6 +21487,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="813">
+      <c r="A813" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B813" t="n">
+        <v>13500</v>
+      </c>
+      <c r="C813" t="n">
+        <v>0.40599998831749</v>
+      </c>
+      <c r="D813" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="E813" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="F813" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G813" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="H813" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -21513,6 +21513,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="814">
+      <c r="A814" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B814" t="n">
+        <v>7500</v>
+      </c>
+      <c r="C814" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="D814" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="E814" t="n">
+        <v>0.40599998831749</v>
+      </c>
+      <c r="F814" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G814" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="H814" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -19094,6 +19094,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="815">
+      <c r="A815" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B815" t="n">
+        <v>0</v>
+      </c>
+      <c r="C815" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="D815" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="E815" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F815" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G815" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B816" t="n">
+        <v>61500</v>
+      </c>
+      <c r="C816" t="n">
+        <v>0.432000011205673</v>
+      </c>
+      <c r="D816" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="E816" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F816"/>
+      <c r="G816" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -21617,6 +21617,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="818">
+      <c r="A818" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B818" t="n">
+        <v>46500</v>
+      </c>
+      <c r="C818" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="D818" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="E818" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F818" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="G818" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="H818" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -19248,8 +19248,31 @@
       <c r="E821" t="n">
         <v>0.430000007152557</v>
       </c>
-      <c r="F821"/>
+      <c r="F821" t="n">
+        <v>0.407999992370605</v>
+      </c>
       <c r="G821" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B822" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C822" t="n">
+        <v>0.404000014066696</v>
+      </c>
+      <c r="D822" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="E822" t="n">
+        <v>0.404000014066696</v>
+      </c>
+      <c r="F822"/>
+      <c r="G822" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -19271,8 +19271,31 @@
       <c r="E822" t="n">
         <v>0.404000014066696</v>
       </c>
-      <c r="F822"/>
+      <c r="F822" t="n">
+        <v>0.395999997854233</v>
+      </c>
       <c r="G822" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B823" t="n">
+        <v>39000</v>
+      </c>
+      <c r="C823" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="D823" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="E823" t="n">
+        <v>0.40599998831749</v>
+      </c>
+      <c r="F823"/>
+      <c r="G823" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -19294,8 +19294,31 @@
       <c r="E823" t="n">
         <v>0.40599998831749</v>
       </c>
-      <c r="F823"/>
+      <c r="F823" t="n">
+        <v>0.40200001001358</v>
+      </c>
       <c r="G823" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B824" t="n">
+        <v>16500</v>
+      </c>
+      <c r="C824" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="D824" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="E824" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="F824"/>
+      <c r="G824" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -19317,8 +19317,31 @@
       <c r="E824" t="n">
         <v>0.40200001001358</v>
       </c>
-      <c r="F824"/>
+      <c r="F824" t="n">
+        <v>0.40200001001358</v>
+      </c>
       <c r="G824" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B825" t="n">
+        <v>54000</v>
+      </c>
+      <c r="C825" t="n">
+        <v>0.430000007152557</v>
+      </c>
+      <c r="D825" t="n">
+        <v>0.388000011444092</v>
+      </c>
+      <c r="E825" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F825"/>
+      <c r="G825" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -19347,6 +19347,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="826">
+      <c r="A826" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B826" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C826" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="D826" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="E826" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="F826" t="n">
+        <v>0.418000012636185</v>
+      </c>
+      <c r="G826" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -19416,6 +19416,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="829">
+      <c r="A829" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B829" t="n">
+        <v>0</v>
+      </c>
+      <c r="C829" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="D829" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="E829" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="F829" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="G829" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -24448,6 +24448,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="831">
+      <c r="A831" t="s">
+        <v>9</v>
+      </c>
+      <c r="B831" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C831" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="D831" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="E831" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="F831" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="G831" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="H831" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I831" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="s">
+        <v>9</v>
+      </c>
+      <c r="B832" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C832" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="D832" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="E832" t="n">
+        <v>0.388000011444092</v>
+      </c>
+      <c r="F832" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="G832" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="H832" t="n">
+        <v>31500</v>
+      </c>
+      <c r="I832" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -24506,6 +24506,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="833">
+      <c r="A833" t="s">
+        <v>9</v>
+      </c>
+      <c r="B833" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C833" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="D833" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E833" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="F833" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="G833" t="n">
+        <v>0.40200001001358</v>
+      </c>
+      <c r="H833" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I833" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -24535,6 +24535,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="834">
+      <c r="A834" t="s">
+        <v>9</v>
+      </c>
+      <c r="B834" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C834" t="n">
+        <v>0.437999993562698</v>
+      </c>
+      <c r="D834" t="n">
+        <v>0.437999993562698</v>
+      </c>
+      <c r="E834" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="F834" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="G834" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="H834" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I834" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -24564,6 +24564,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="835">
+      <c r="A835" t="s">
+        <v>9</v>
+      </c>
+      <c r="B835" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C835" t="n">
+        <v>0.428000003099442</v>
+      </c>
+      <c r="D835" t="n">
+        <v>0.428000003099442</v>
+      </c>
+      <c r="E835" t="n">
+        <v>0.40599998831749</v>
+      </c>
+      <c r="F835" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="G835" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="H835" t="n">
+        <v>36000</v>
+      </c>
+      <c r="I835" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -24593,6 +24593,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="836">
+      <c r="A836" t="s">
+        <v>9</v>
+      </c>
+      <c r="B836" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C836" t="n">
+        <v>0.40599998831749</v>
+      </c>
+      <c r="D836" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="E836" t="n">
+        <v>0.377999991178513</v>
+      </c>
+      <c r="F836" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="G836" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="H836" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I836" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -24622,6 +24622,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="837">
+      <c r="A837" t="s">
+        <v>9</v>
+      </c>
+      <c r="B837" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C837" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="D837" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="E837" t="n">
+        <v>0.412000000476837</v>
+      </c>
+      <c r="F837" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="G837" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="H837" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I837" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -24651,6 +24651,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="838">
+      <c r="A838" t="s">
+        <v>9</v>
+      </c>
+      <c r="B838" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C838" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="D838" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="E838" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="F838" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="G838" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="H838" t="n">
+        <v>24000</v>
+      </c>
+      <c r="I838" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GRN.MI.xlsx
+++ b/data/GRN.MI.xlsx
@@ -24680,6 +24680,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="839">
+      <c r="A839" t="s">
+        <v>9</v>
+      </c>
+      <c r="B839" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C839" t="n">
+        <v>0.416000008583069</v>
+      </c>
+      <c r="D839" t="n">
+        <v>0.419999986886978</v>
+      </c>
+      <c r="E839" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F839" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="G839" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="H839" t="n">
+        <v>51000</v>
+      </c>
+      <c r="I839" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
